--- a/InputData/ccs/SoCTaSCbRIC/Share of CCS Transportation and Storage Costs by Recipient ISIC Code.xlsx
+++ b/InputData/ccs/SoCTaSCbRIC/Share of CCS Transportation and Storage Costs by Recipient ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ccs\SoCTaSCbRIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\SoCTaSCbRIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1B974E-C82B-4AFB-A807-68E97D691590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FCE592-33B9-486D-B154-CA1C60C6FB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="2" r:id="rId1"/>
@@ -230,16 +230,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,38 +517,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
